--- a/Result/checksun_type/光源_磊晶.xlsx
+++ b/Result/checksun_type/光源_磊晶.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>105</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>103180579.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>116147614.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>116147614.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>176548720.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>201428975.56</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>201428975.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-25860202.92993152</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>103180579</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>103180579.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>98.94</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>103.24</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>105.06</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>105.06</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>78066930.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>134482037.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>134482037.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>193869170.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>205225010.12</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>205225010.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-24317788.82020301</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>78066930</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>78066930.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>98.72</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>103.7</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>105.23</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>105.23</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>136094275.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>162561404.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>162561404.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>195664628.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>209197245.52</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>209197245.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-18555099.52701217</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>136094275</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>136094275.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>98.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>104.3</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>105.44</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>105.44</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>116900919.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>222301963.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>222301963.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>191158060.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>220229469.28</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>220229469.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-15877219.6607748</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>116900919</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>116900919.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>99.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>104.8</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>105.6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>146495369.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>240594220.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>240594220.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>198554746.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>221461486.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>221461486.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-9428202.435408056</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>146495369</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>146495369.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>100.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>105.28</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>105.69</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>105.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>194852695.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>236949826.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>236949826.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>211794368.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>221171326.8</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>221171326.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-3049433.097905278</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>194852695</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>194852695.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>101.84</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>105.84</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>105.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>218463765.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>253256304.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>253256304</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>212975569.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>219688213.02</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>219688213.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>990860.7805953324</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>218463765</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>102.86</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>106</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>434797068.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>228767852.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>230869656.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>217695178.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>4197563.793432087</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>434797068</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>434797068.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>103.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>106.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>106.11</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>106.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>208362204.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>160014158.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>160014158.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>237292886.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>210329621.68</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>210329621.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-14549913.0737094</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>208362204</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>106.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>128273399.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>156515273.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>280273763.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>208482988.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-16551504.84556478</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>128273399</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>128273399.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>106.85</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>106.24</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>276385084.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>186638909.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>186638909.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>285043227.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>208948816.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>208948816.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-10238853.09658802</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>276385084</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>276385084.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>121.5</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>123.98</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>119.29</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>123.98</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>119.29</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>116792257.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>156567321.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>156567321.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>189454064.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>318150407.34</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>318150407.34</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-35640807.2288911</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>116792257</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>116792257.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>123.78</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>119.06</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>119.06</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>143570356.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>190225454.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>190225454.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>215742345.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>318733821.76</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>318733821.76</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-33370636.02417654</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>143570356</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>143570356.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>120.8</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>118.88</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>118.88</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>136096754.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>206130143.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>206130143.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>221377285.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>318478020.68</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>318478020.68</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-31804807.90943512</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>136096754</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>136096754.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>118.73</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>118.73</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>166072395.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>203391625.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>203391625.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>240690842.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>318219735.08</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>318219735.08</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-27631281.53446758</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>166072395</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>166072395.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>122.3</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>118.63</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>118.63</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>220304845.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>213645726.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>213645726</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>249224824.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>318339495.48</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>318339495.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-23893945.33685437</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>220304845</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>220304845.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>123.6</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>123.42</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>118.47</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>123.42</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>118.47</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>285082922.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>222340807.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>222340807.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>250119491.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>316878790.8</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>316878790.8</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-23512158.07823354</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>285082922</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>285082922.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>124.6</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>123.1</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>118.31</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>118.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>223093801.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>241259236.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>241259236.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>251423710.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>315242401.56</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>315242401.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-29067536.02740973</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>223093801</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>223093801.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>125.6</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>122.78</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>118.16</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>122.78</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>118.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>122404164.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>236624427.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>236624427.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>278228999.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>313300516.2</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>313300516.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-29323972.41811109</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>122404164</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>122404164.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>126.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>122.28</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>117.91</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>122.28</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>117.91</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>217342898.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>277990060.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>277990060</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>338438970.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>312973362.38</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>312973362.38</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-17854849.99703753</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>217342898</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>217342898.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>125.4</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>121.6</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>117.66</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>117.66</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>263780252.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>284803923.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>284803923.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>409270685.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>312412010.72</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>312412010.72</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-11004723.39560974</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>263780252</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>263780252.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>125.2</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>120.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>117.36</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>120.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>117.36</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>379675068.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>277898176.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>277898176.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>437448534.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>311595701.46</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>311595701.46</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-5801233.20086962</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>379675068</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>379675068.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>20.18</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>20.09</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>244.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>272.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>272</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>304.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-127.6786566908388</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>244</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>244.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>20.08</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>19.88</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>20.1</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>162.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>275.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>275.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>457.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-134.897043662929</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>162</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>19.96</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>20.1</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>220.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>361.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>361.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>591.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-131.6055592065246</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>220</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>19.92</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>20.11</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>355.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>357.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>357.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>587.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-128.4175257257139</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>355</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>355.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>19.92</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>20.12</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>20.12</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>379.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>311.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>311.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>560.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-133.7411376914945</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>379</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>379.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>19.91</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>260.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>336.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>336.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>562.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-139.1412570107706</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>260</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>260.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>19.94</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>20.16</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>595.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>639.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>639.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-129.1363825736374</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>595</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>595.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>20.04</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>20.18</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>20.18</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>200.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>821.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>821.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-146.1245482858174</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>200</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>20.06</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>20.2</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>818.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>818</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-122.8531940072952</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>122</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>20.08</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>19.77</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>20.22</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>20.22</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>505.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>809.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>809.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-76.86364525200281</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>505</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>505.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>20.12</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>20.24</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>20.24</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>1777.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>787.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>787.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-49.4548739854423</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1777</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1777.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>18.5</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>19.82</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>19.82</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>29634391.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>9747051.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>9747051.199999999</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>7913835.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>11092022.78</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>11092022.78</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>984593.8377851136</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>29634391</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>29634391.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>18.08</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>18.68</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>19.84</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>19.84</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>4003242.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>5189211.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>5189211.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>6326445.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>10789601.46</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>10789601.46</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-921404.894587703</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>4003242</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>4003242.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>18.12</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>19.9</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>4455562.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>5628153.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>5628153.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>6991779.1</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>10984592.32</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>10984592.32</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-865158.3731707362</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>4455562</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>4455562.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>18.39</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>18.83</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>19.98</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>19.98</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>5789019.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>5707756.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>5707756.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>7422229.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>11128571.86</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>11128571.86</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-802370.5435332581</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>5789019</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>5789019.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>18.67</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>20.07</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>20.07</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>4853042.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>5385160.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>5385160.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>7385873.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>11334557.36</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>11334557.36</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-826887.9460678147</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>4853042</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>4853042.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>18.81</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>6845191.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>6080619.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>6080619.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>7487884.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>11330661.82</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>11330661.82</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-732097.8444719044</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>6845191</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>6845191.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>19.08</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>20.2</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>6197954.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>7463679.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>7463679.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>7632465.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>11356821.32</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>11356821.32</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-783981.5977466069</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>6197954</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>6197954.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>19.11</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>19.13</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>20.26</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>4853578.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>8355404.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>8355404.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>7956112.4</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>11416994.32</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>11416994.32</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-760755.0810766593</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>4853578</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>4853578.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>18.88</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>19.14</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>20.3</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>20.3</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>4176036.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>9136703.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>9136703</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>8396717.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>11685903.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>11685903</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-556364.2329382822</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>4176036</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>4176036.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>18.68</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>19.18</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>20.34</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>8330339.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>9386586.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>9386586.800000001</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>9260349.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>12020532.38</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>12020532.38</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-171913.3701356612</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>8330339</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>8330339.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>18.57</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>20.41</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>20.41</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>13760492.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>8895150.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>8895150</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>9737781.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>13101208.8</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>13101208.8</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-61661.98148421571</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>13760492</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>13760492.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>201.9</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>226.95</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>227.58</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>226.95</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>227.58</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>90663.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>114762.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>114762.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>123500.7</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>273993.44</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>273993.44</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-31215.27260816598</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>90663</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>90663.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>201.8</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>229.72</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>227.19</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>229.72</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>227.19</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>93169.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>125649.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>125649</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>130618.1</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>283082.9</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>283082.9</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-30570.17550505494</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>93169</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>93169.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>203.4</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>232.6</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>227.0</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>227</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>90567.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>147137.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>147137.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>171768.1</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>285167.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>285167.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-28825.31623257286</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>90567</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>90567.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>207.2</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>235.9</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>226.52</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>235.9</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>226.52</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>188545.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>150672.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>150672.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>224103.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>291936.48</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>291936.48</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-25024.39883500661</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>188545</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>188545.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>212.5</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>239.08</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>226.07</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>239.08</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>226.07</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>110870.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>128416.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>128416</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>221540.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>295295.0</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>295295</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-29198.43116580459</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>110870</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>110870.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>216.9</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>241.65</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>225.09</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>241.65</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>225.09</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>145094.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>132238.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>132238.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>233985.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>294618.16</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>294618.16</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-25796.21195388012</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>145094</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>145094.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>221.3</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>244.6</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>224.17</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>244.6</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>224.17</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>200610.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>135587.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>135587.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>249984.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>295031.98</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>295031.98</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-23681.46265277802</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>200610</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>200610.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>223.5</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>247.42</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>223.12</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>247.42</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>223.12</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>108244.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>196399.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>196399</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>271350.4</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>291675.48</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>291675.48</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-25762.76855646149</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>108244</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>108244.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>228.8</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>249.28</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>221.94</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>249.28</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>221.94</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>77262.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>297534.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>297534</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>296942.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>290061.26</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>290061.26</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-17919.60668470713</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>77262</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>77262.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>234.0</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>250.9</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>220.66</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>220.66</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>129983.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>314664.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>314664.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>313434.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>289641.36</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>289641.36</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-2755.603772032773</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>129983</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>129983.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>237.4</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>252.08</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>219.29</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>252.08</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>219.29</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>161837.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>335733.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>335733</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>325527.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>288207.54</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>288207.54</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>13356.99338078895</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>161837</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>161837.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>31.41</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>33.02</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>36.04</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>36.04</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>24395745.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>43484631.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>43484631.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>45615664.0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>82073847.42</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>82073847.42</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-3013497.008108601</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>24395745</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>24395745.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>31.34</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>36.16</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>36.16</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>30014784.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>49686517.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>49686517.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>48929446.0</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>84374614.76</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>84374614.76000001</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-1295917.162061319</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>30014784</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>30014784.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>31.41</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>33.39</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>36.3</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>36.3</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>74106859.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>57898938.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>57898938</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>51636052.3</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>85756084.54</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>85756084.54000001</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>602011.1952226907</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>74106859</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>74106859.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>31.89</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>33.66</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>36.44</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>36.44</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>58993955.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>50545739.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>50545739.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>49632148.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>85889781.46</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>85889781.45999999</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-1432313.872772388</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>58993955</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>58993955.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>32.33</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>33.89</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>36.58</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>36.58</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>29911815.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>47720986.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>47720986.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>46300654.5</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>86650683.62</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>86650683.62</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-2668098.76016634</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>29911815</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>29911815.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>32.73</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>34.11</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>36.68</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>36.68</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>55405176.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>47746696.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>47746696.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>47463558.6</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>87062980.58</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>87062980.58</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-1222272.929294623</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>55405176</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>55405176.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>33.25</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>36.81</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>71076885.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>48172374.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>48172374.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>46480647.2</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>87345637.88</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>87345637.88</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-1844586.387717366</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>71076885</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>71076885.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>33.51000000000001</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>34.58</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>36.94</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>36.94</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>37340866.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>45373166.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>45373166.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>44436752.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>87105935.02</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>87105935.02</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-4346839.207331359</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>37340866</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>37340866.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>33.56</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>34.73</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>37.04</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>34.73</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>37.04</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>44870190.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>48718557.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>48718557</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>44808975.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>88161860.3</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>88161860.3</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-4151668.370803811</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>44870190</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>44870190.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>33.72</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>34.89</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>37.13</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>37.13</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>30040365.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>44880322.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>44880322.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>46778158.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>89186868.04</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>89186868.04000001</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-4531292.305378608</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>30040365</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>30040365.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>33.77</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>34.99</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>37.23</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>37.23</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>57533565.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>47180420.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>47180420.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>50051671.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>93415845.44</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>93415845.44</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-3322870.522436216</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>57533565</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>57533565.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>24.72</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>26.54</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>29.79</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>29.79</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>5272.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>6124.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>6124.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>11113.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>30306.14</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>30306.14</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-2039.678450840738</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>5272</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>5272.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>24.63</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>26.71</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>29.96</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>29.96</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>2297.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>7466.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>7466.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>11388.6</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>31240.84</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>31240.84</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-1971.738541865034</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>2297</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>2297.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>24.81</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>26.9</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>30.12</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>30.12</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>6314.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>12477.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>12477.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>12145.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>31759.26</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>31759.26</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-1485.512295404562</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>6314</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>6314.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>25.02</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>27.08</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>30.31</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>30.31</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>8277.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>12766.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>12766</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>12403.6</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>32334.02</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>32334.02</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-1168.242218482297</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>8277</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>8277.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>25.41</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>27.32</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>30.51</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>30.51</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>8464.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>14736.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>14736.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>12627.3</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>32482.12</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>32482.12</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-883.5977436475514</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>8464</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>8464.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>25.89</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>30.68</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>30.68</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>11979.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>16102.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>16102.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>12477.5</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>33240.98</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>33240.98</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-465.4414316105049</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>11979</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>11979.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>26.48</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>27.73</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>30.84</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>30.84</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>27353.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>15311.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>15311</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>12535.0</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>33532.12</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>33532.12</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-228.0595061429194</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>27353</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>27353.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>26.84</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>27.87</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>30.98</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>30.98</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>7757.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>11814.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>11814.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>10696.4</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>33317.42</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>33317.42</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-1528.01177311269</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>7757</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>7757.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>27.16</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>28.04</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>31.12</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>31.12</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>18128.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>12041.2</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>12041.2</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>12870.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>33680.84</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>33680.84</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-1230.943162601196</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>18128</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>18128.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>27.57</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>28.19</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>31.27</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>31.27</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>15295.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>10518.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>10518.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>16175.9</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>33836.9</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>33836.9</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-1873.775748920449</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>15295</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>15295.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>27.64</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>28.26</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>31.42</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>31.42</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>8022.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>8852.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>8852.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>15760.8</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>34296.52</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>34296.52</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-2421.651738343648</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>8022</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>8022.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>13.56</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>13.16</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>14268504.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>7249024.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>7249024</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>4013502.5</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>1806762.58</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>1806762.58</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>1860277.105062644</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>14268504</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>14268504.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>13.77</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>13.48</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>13.13</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>13.13</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>19324917.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>4474500.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>4474500.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>2680782.5</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>1559186.4</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>1559186.4</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>1298075.861681122</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>19324917</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>19324917.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>13.6</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>13.42</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>13.12</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>13.12</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>747352.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>738435.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>738435.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>889759.3</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>1194825.0</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>1194825</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-93187.15963823383</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>747352</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>747352.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>13.73</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>13.44</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>13.13</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>13.13</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>890136.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>963018.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>963018</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1200071.4</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>1209385.54</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>1209385.54</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-86924.25582166249</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>890136</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>890136.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>13.72</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>13.14</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>13.14</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1014211.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>826858.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>826858.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1204934.9</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1209173.9</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1209173.9</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-90171.0983757868</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1014211</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1014211.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>13.76</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>13.36</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>13.15</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>395887.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>777981.0</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>777981</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1295516.0</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>1214275.24</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>1214275.24</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-104882.7985111149</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>395887</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>395887.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>13.84</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>13.16</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>644591.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>887064.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>887064.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1310132.0</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>1256904.46</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>1256904.46</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-55904.69875761541</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>644591</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>644591.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>13.8</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>13.18</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>13.18</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>1870265.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1041083.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1041083.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1295875.5</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>1300658.24</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>1300658.24</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-10586.24558270094</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1870265</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1870265.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>13.74</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>13.17</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>13.17</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>209340.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1437124.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1437124.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1160130.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>1291148.76</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>1291148.76</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-76789.73227629834</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>209340</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>209340.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>13.68</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>13.17</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>13.17</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>769822.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1583011.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1583011</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1216033.9</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>1347530.0</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>1347530</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>9332.598599859048</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>769822</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>769822.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>13.56</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>13.02</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>13.19</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>13.19</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>941304.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1813051.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1813051</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1258842.7</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>1473262.06</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>1473262.06</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>71979.5499015178</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>941304</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>941304.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>23.63</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>26.01</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>69398365.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>46175655.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>46175655.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>40727993.5</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>194676121.56</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>194676121.56</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-6011750.455637693</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>69398365</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>69398365.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>24.49</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>40606624.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>40014316.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>40014316.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>41687883.7</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>195169236.84</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>195169236.84</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-9065902.528399438</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>40606624</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>40606624.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>23.48</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>25.97</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>33681849.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>39637812.8</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>39637812.8</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>51965661.4</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>195984000.1</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>195984000.1</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-10020365.29204483</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>33681849</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>33681849.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>23.88</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>49106509.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>38566967.2</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>38566967.2</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>52615128.9</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>195992723.02</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>195992723.02</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-10284073.15825091</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>49106509</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>49106509.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>24.26</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>38084932.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>35331650.4</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>35331650.4</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>52705529.4</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>195762947.24</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>195762947.24</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-11946152.49717921</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>38084932</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>38084932.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>24.53</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>25.95</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>38591667.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>35280331.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>35280331.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>51774555.3</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>196053683.56</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>196053683.56</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-12713019.99932038</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>38591667</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>38591667.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>25.11</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>25.96</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>38724107.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>43361451.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>43361451.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>53384515.1</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>197488634.64</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>197488634.64</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-13408801.60954632</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>38724107</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>38724107.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>25.59</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>25.94</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>25.94</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>28327621.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>64293510.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>64293510</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>53134957.6</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>197699079.6</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>197699079.6</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-13938079.56667101</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>28327621</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>28327621.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>25.52</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>25.88</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>32929925.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>66663290.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>66663290.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>54706545.9</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>197755621.26</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>197755621.26</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-13082493.16375375</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>32929925</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>32929925.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>37828336.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>70079408.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>70079408.40000001</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>58159640.7</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>197616845.6</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>197616845.6</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-11886098.97516645</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>37828336</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>37828336.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>25.03</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>25.76</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>78997267.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>68268779.4</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>68268779.40000001</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>64193506.3</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>197596036.22</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>197596036.22</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-10277290.63521439</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>78997267</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>78997267.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
